--- a/data_pencairan1.xlsx
+++ b/data_pencairan1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\ProjectMap-master\ProjectMap-master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\ProjectMap-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E3476D-25D1-4741-A4ED-28AD6D7BF6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5795DBF7-26EF-4E85-827E-8E1475015800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{54E22A41-8FC8-4C9D-8F0D-924CB0D9AAAD}"/>
   </bookViews>
@@ -268,9 +268,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -308,7 +308,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -414,7 +414,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -556,7 +556,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -632,40 +632,40 @@
         <v>0</v>
       </c>
       <c r="C2" s="2">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1">
+        <v>111751733</v>
+      </c>
+      <c r="E2" s="1">
         <v>22</v>
       </c>
-      <c r="D2" s="1">
-        <v>85297334</v>
-      </c>
-      <c r="E2" s="2">
-        <v>32</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>11</v>
-      </c>
-      <c r="K2" s="2">
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1">
         <v>0</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" s="2">
-        <v>4</v>
+      <c r="M2" s="1">
+        <v>1</v>
       </c>
       <c r="N2" s="1">
-        <v>15237066</v>
+        <v>1724724</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -676,40 +676,40 @@
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1">
-        <v>463965711</v>
-      </c>
-      <c r="E3" s="2">
-        <v>565</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2">
-        <v>5</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>56</v>
-      </c>
-      <c r="K3" s="2">
+        <v>371496462</v>
+      </c>
+      <c r="E3" s="1">
+        <v>440</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>24</v>
+        <v>2548179</v>
+      </c>
+      <c r="M3" s="1">
+        <v>23</v>
       </c>
       <c r="N3" s="1">
-        <v>114264332</v>
+        <v>89844936</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -720,40 +720,40 @@
         <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1">
-        <v>117144180</v>
-      </c>
-      <c r="E4" s="2">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
+        <v>75829051</v>
+      </c>
+      <c r="E4" s="1">
+        <v>44</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>4</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
       </c>
-      <c r="M4" s="2">
-        <v>4</v>
+      <c r="M4" s="1">
+        <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>25093959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -764,40 +764,40 @@
         <v>47</v>
       </c>
       <c r="C5" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1">
-        <v>37718685</v>
-      </c>
-      <c r="E5" s="2">
-        <v>39</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>17</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
+        <v>19417469</v>
+      </c>
+      <c r="E5" s="1">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>14</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
+        <v>3647872</v>
+      </c>
+      <c r="M5" s="1">
         <v>4</v>
       </c>
       <c r="N5" s="1">
-        <v>23228501</v>
+        <v>2733164</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -808,40 +808,40 @@
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="D6" s="1">
-        <v>1053565993</v>
-      </c>
-      <c r="E6" s="2">
-        <v>989</v>
-      </c>
-      <c r="F6" s="2">
+        <v>919079588</v>
+      </c>
+      <c r="E6" s="1">
+        <v>818</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="G6" s="2">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2">
-        <v>123</v>
-      </c>
-      <c r="K6" s="2">
-        <v>4</v>
+      <c r="J6" s="1">
+        <v>83</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>2662431</v>
-      </c>
-      <c r="M6" s="2">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>39</v>
       </c>
       <c r="N6" s="1">
-        <v>206450834</v>
+        <v>148541643</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -852,40 +852,40 @@
         <v>4</v>
       </c>
       <c r="C7" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1">
-        <v>65397022</v>
-      </c>
-      <c r="E7" s="2">
-        <v>65</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>9</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
+        <v>149934074</v>
+      </c>
+      <c r="E7" s="1">
+        <v>41</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>4</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
-      <c r="M7" s="2">
-        <v>1</v>
+      <c r="M7" s="1">
+        <v>2</v>
       </c>
       <c r="N7" s="1">
-        <v>2658390</v>
+        <v>17718353</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -896,40 +896,40 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D8" s="1">
-        <v>727622687</v>
-      </c>
-      <c r="E8" s="2">
-        <v>153</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2">
-        <v>5</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>16</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
+        <v>730085994</v>
+      </c>
+      <c r="E8" s="1">
+        <v>106</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>10977121</v>
-      </c>
-      <c r="M8" s="2">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>12</v>
       </c>
       <c r="N8" s="1">
-        <v>66235796</v>
+        <v>56108460</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -940,38 +940,40 @@
         <v>6</v>
       </c>
       <c r="C9" s="2">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="D9" s="1">
-        <v>917584681</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1117</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2">
-        <v>6</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>139</v>
-      </c>
-      <c r="K9" s="2">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="2">
-        <v>56</v>
+        <v>649017456</v>
+      </c>
+      <c r="E9" s="1">
+        <v>797</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>7</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>109</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>45</v>
       </c>
       <c r="N9" s="1">
-        <v>218964968</v>
+        <v>204718176</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -982,40 +984,40 @@
         <v>7</v>
       </c>
       <c r="C10" s="2">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1">
-        <v>705585871</v>
-      </c>
-      <c r="E10" s="2">
-        <v>351</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
+        <v>749261368</v>
+      </c>
+      <c r="E10" s="1">
+        <v>283</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>35</v>
+      </c>
+      <c r="K10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>70</v>
-      </c>
-      <c r="K10" s="2">
-        <v>5</v>
-      </c>
       <c r="L10" s="1">
-        <v>30748891</v>
-      </c>
-      <c r="M10" s="2">
-        <v>24</v>
+        <v>11953560</v>
+      </c>
+      <c r="M10" s="1">
+        <v>19</v>
       </c>
       <c r="N10" s="1">
-        <v>64322553</v>
+        <v>80019490</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1026,40 +1028,40 @@
         <v>8</v>
       </c>
       <c r="C11" s="2">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="D11" s="1">
-        <v>680514871</v>
-      </c>
-      <c r="E11" s="2">
-        <v>478</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>13</v>
-      </c>
-      <c r="H11" s="2">
+        <v>522025703</v>
+      </c>
+      <c r="E11" s="1">
+        <v>351</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>89</v>
-      </c>
-      <c r="K11" s="2">
-        <v>3</v>
+      <c r="H11" s="1">
+        <v>7</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>59</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>36</v>
+        <v>10097573</v>
+      </c>
+      <c r="M11" s="1">
+        <v>34</v>
       </c>
       <c r="N11" s="1">
-        <v>141039403</v>
+        <v>119316146</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1070,40 +1072,40 @@
         <v>9</v>
       </c>
       <c r="C12" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="D12" s="1">
-        <v>1746927895</v>
-      </c>
-      <c r="E12" s="2">
-        <v>204</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
+        <v>685972225</v>
+      </c>
+      <c r="E12" s="1">
+        <v>123</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>9</v>
+      </c>
+      <c r="K12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" s="2">
-        <v>34</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>25</v>
-      </c>
-      <c r="K12" s="2">
-        <v>8</v>
-      </c>
       <c r="L12" s="1">
-        <v>37302519</v>
-      </c>
-      <c r="M12" s="2">
-        <v>31</v>
+        <v>9447629</v>
+      </c>
+      <c r="M12" s="1">
+        <v>9</v>
       </c>
       <c r="N12" s="1">
-        <v>196097326</v>
+        <v>65038503</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1114,40 +1116,40 @@
         <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1">
-        <v>424697078</v>
-      </c>
-      <c r="E13" s="2">
-        <v>116</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
+        <v>216990010</v>
+      </c>
+      <c r="E13" s="1">
+        <v>79</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
         <v>4</v>
       </c>
-      <c r="H13" s="2">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>17</v>
-      </c>
-      <c r="K13" s="2">
-        <v>2</v>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>13</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>6414511</v>
-      </c>
-      <c r="M13" s="2">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4</v>
       </c>
       <c r="N13" s="1">
-        <v>28194088</v>
+        <v>31936984</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1158,40 +1160,40 @@
         <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="D14" s="1">
-        <v>2020651562</v>
-      </c>
-      <c r="E14" s="2">
-        <v>201</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>6</v>
-      </c>
-      <c r="H14" s="2">
-        <v>19</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <v>16</v>
-      </c>
-      <c r="K14" s="2">
-        <v>3</v>
+        <v>1121607406</v>
+      </c>
+      <c r="E14" s="1">
+        <v>152</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>12</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>13748301</v>
-      </c>
-      <c r="M14" s="2">
-        <v>15</v>
+        <v>23901708</v>
+      </c>
+      <c r="M14" s="1">
+        <v>10</v>
       </c>
       <c r="N14" s="1">
-        <v>93463587</v>
+        <v>67189427</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1202,40 +1204,40 @@
         <v>12</v>
       </c>
       <c r="C15" s="2">
-        <v>1238</v>
+        <v>920</v>
       </c>
       <c r="D15" s="1">
-        <v>15579777370</v>
-      </c>
-      <c r="E15" s="2">
-        <v>733</v>
-      </c>
-      <c r="F15" s="2">
-        <v>3</v>
-      </c>
-      <c r="G15" s="2">
-        <v>38</v>
-      </c>
-      <c r="H15" s="2">
-        <v>231</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>29</v>
-      </c>
-      <c r="K15" s="2">
-        <v>21</v>
+        <v>12808340548</v>
+      </c>
+      <c r="E15" s="1">
+        <v>584</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>23</v>
+      </c>
+      <c r="H15" s="1">
+        <v>180</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>15</v>
+      </c>
+      <c r="K15" s="1">
+        <v>8</v>
       </c>
       <c r="L15" s="1">
-        <v>118577548</v>
-      </c>
-      <c r="M15" s="2">
-        <v>107</v>
+        <v>26711628</v>
+      </c>
+      <c r="M15" s="1">
+        <v>57</v>
       </c>
       <c r="N15" s="1">
-        <v>791450709</v>
+        <v>449931777</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1246,40 +1248,40 @@
         <v>13</v>
       </c>
       <c r="C16" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D16" s="1">
-        <v>1358105264</v>
-      </c>
-      <c r="E16" s="2">
-        <v>87</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>7</v>
-      </c>
-      <c r="H16" s="2">
-        <v>57</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2">
+        <v>1640398974</v>
+      </c>
+      <c r="E16" s="1">
+        <v>66</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>36</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1">
         <v>0</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
       </c>
-      <c r="M16" s="2">
-        <v>15</v>
+      <c r="M16" s="1">
+        <v>9</v>
       </c>
       <c r="N16" s="1">
-        <v>86157510</v>
+        <v>71747323</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1290,40 +1292,40 @@
         <v>48</v>
       </c>
       <c r="C17" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>24500000</v>
-      </c>
-      <c r="E17" s="2">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>3</v>
-      </c>
-      <c r="K17" s="2">
+        <v>71568131</v>
+      </c>
+      <c r="E17" s="1">
+        <v>22</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
       </c>
-      <c r="M17" s="2">
-        <v>1</v>
+      <c r="M17" s="1">
+        <v>2</v>
       </c>
       <c r="N17" s="1">
-        <v>629750</v>
+        <v>2616477</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1334,40 +1336,40 @@
         <v>43</v>
       </c>
       <c r="C18" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D18" s="1">
-        <v>157798101</v>
-      </c>
-      <c r="E18" s="2">
-        <v>73</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
+        <v>154169849</v>
+      </c>
+      <c r="E18" s="1">
+        <v>31</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
         <v>2</v>
       </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>11</v>
-      </c>
-      <c r="K18" s="2">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>8</v>
+      </c>
+      <c r="K18" s="1">
         <v>0</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
       </c>
-      <c r="M18" s="2">
-        <v>3</v>
+      <c r="M18" s="1">
+        <v>8</v>
       </c>
       <c r="N18" s="1">
-        <v>16493074</v>
+        <v>20157986</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1378,40 +1380,40 @@
         <v>14</v>
       </c>
       <c r="C19" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>70225877</v>
-      </c>
-      <c r="E19" s="2">
-        <v>77</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
+        <v>96101951</v>
+      </c>
+      <c r="E19" s="1">
+        <v>68</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
         <v>2</v>
       </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>13</v>
-      </c>
-      <c r="K19" s="2">
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>8</v>
+      </c>
+      <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
       </c>
-      <c r="M19" s="2">
-        <v>8</v>
+      <c r="M19" s="1">
+        <v>3</v>
       </c>
       <c r="N19" s="1">
-        <v>23881272</v>
+        <v>13195278</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1422,40 +1424,40 @@
         <v>15</v>
       </c>
       <c r="C20" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1">
-        <v>62400451</v>
-      </c>
-      <c r="E20" s="2">
-        <v>35</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>6</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
+        <v>18043767</v>
+      </c>
+      <c r="E20" s="1">
+        <v>28</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>10</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>7120929</v>
-      </c>
-      <c r="M20" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>5</v>
       </c>
       <c r="N20" s="1">
-        <v>1720276</v>
+        <v>25112000</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1466,40 +1468,40 @@
         <v>16</v>
       </c>
       <c r="C21" s="2">
-        <v>1460</v>
+        <v>19</v>
       </c>
       <c r="D21" s="1">
-        <v>29563771879</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1104</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2">
-        <v>21</v>
-      </c>
-      <c r="H21" s="2">
-        <v>73</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>53</v>
-      </c>
-      <c r="K21" s="2">
-        <v>9</v>
+        <v>277625931</v>
+      </c>
+      <c r="E21" s="1">
+        <v>75</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>19</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>16</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
       </c>
       <c r="L21" s="1">
-        <v>10804677</v>
-      </c>
-      <c r="M21" s="2">
-        <v>75</v>
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>6</v>
       </c>
       <c r="N21" s="1">
-        <v>260249589</v>
+        <v>36724597</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1510,40 +1512,40 @@
         <v>44</v>
       </c>
       <c r="C22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>3</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
         <v>0</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
       </c>
-      <c r="M22" s="2">
-        <v>0</v>
+      <c r="M22" s="1">
+        <v>2</v>
       </c>
       <c r="N22" s="1">
-        <v>0</v>
+        <v>9941022</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -1554,40 +1556,40 @@
         <v>17</v>
       </c>
       <c r="C23" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D23" s="1">
-        <v>54455687</v>
-      </c>
-      <c r="E23" s="2">
-        <v>36</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>12</v>
-      </c>
-      <c r="K23" s="2">
+        <v>8570693</v>
+      </c>
+      <c r="E23" s="1">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1">
         <v>0</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
-      <c r="M23" s="2">
-        <v>6</v>
+      <c r="M23" s="1">
+        <v>2</v>
       </c>
       <c r="N23" s="1">
-        <v>25167026</v>
+        <v>9759632</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -1598,40 +1600,40 @@
         <v>18</v>
       </c>
       <c r="C24" s="2">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1">
-        <v>280852335</v>
-      </c>
-      <c r="E24" s="2">
-        <v>53</v>
-      </c>
-      <c r="F24" s="2">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>2</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
-        <v>16</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0</v>
+        <v>41325589</v>
+      </c>
+      <c r="E24" s="1">
+        <v>32</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>10</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
       </c>
-      <c r="M24" s="2">
-        <v>7</v>
+      <c r="M24" s="1">
+        <v>4</v>
       </c>
       <c r="N24" s="1">
-        <v>22217212</v>
+        <v>14025246</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1642,40 +1644,40 @@
         <v>19</v>
       </c>
       <c r="C25" s="2">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="D25" s="1">
-        <v>1467238022</v>
-      </c>
-      <c r="E25" s="2">
-        <v>147</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>3</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>28</v>
-      </c>
-      <c r="K25" s="2">
-        <v>6</v>
+        <v>712235515</v>
+      </c>
+      <c r="E25" s="1">
+        <v>98</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>22</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
       </c>
       <c r="L25" s="1">
-        <v>20282028</v>
-      </c>
-      <c r="M25" s="2">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>11</v>
       </c>
       <c r="N25" s="1">
-        <v>96569946</v>
+        <v>70144837</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1686,40 +1688,40 @@
         <v>20</v>
       </c>
       <c r="C26" s="2">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1">
-        <v>350156824</v>
-      </c>
-      <c r="E26" s="2">
-        <v>102</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>3</v>
-      </c>
-      <c r="H26" s="2">
-        <v>7</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <v>13</v>
-      </c>
-      <c r="K26" s="2">
+        <v>82689589</v>
+      </c>
+      <c r="E26" s="1">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>2259285</v>
-      </c>
-      <c r="M26" s="2">
-        <v>10</v>
+        <v>3949602</v>
+      </c>
+      <c r="M26" s="1">
+        <v>1</v>
       </c>
       <c r="N26" s="1">
-        <v>37983799</v>
+        <v>9693674</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1730,40 +1732,40 @@
         <v>21</v>
       </c>
       <c r="C27" s="2">
-        <v>663</v>
+        <v>521</v>
       </c>
       <c r="D27" s="1">
-        <v>5795375117</v>
-      </c>
-      <c r="E27" s="2">
-        <v>796</v>
-      </c>
-      <c r="F27" s="2">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2">
-        <v>22</v>
-      </c>
-      <c r="H27" s="2">
-        <v>50</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
-        <v>76</v>
-      </c>
-      <c r="K27" s="2">
-        <v>4</v>
+        <v>4673091085</v>
+      </c>
+      <c r="E27" s="1">
+        <v>589</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6</v>
+      </c>
+      <c r="H27" s="1">
+        <v>38</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>38</v>
+      </c>
+      <c r="K27" s="1">
+        <v>5</v>
       </c>
       <c r="L27" s="1">
-        <v>29577706</v>
-      </c>
-      <c r="M27" s="2">
-        <v>104</v>
+        <v>28974792</v>
+      </c>
+      <c r="M27" s="1">
+        <v>48</v>
       </c>
       <c r="N27" s="1">
-        <v>629592931</v>
+        <v>257137301</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1777,37 +1779,37 @@
         <v>10</v>
       </c>
       <c r="D28" s="1">
-        <v>59091657</v>
-      </c>
-      <c r="E28" s="2">
-        <v>16</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
-        <v>5</v>
-      </c>
-      <c r="K28" s="2">
+        <v>51814579</v>
+      </c>
+      <c r="E28" s="1">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1">
         <v>0</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
       </c>
-      <c r="M28" s="2">
-        <v>2</v>
+      <c r="M28" s="1">
+        <v>4</v>
       </c>
       <c r="N28" s="1">
-        <v>695312</v>
+        <v>20251816</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1818,40 +1820,40 @@
         <v>23</v>
       </c>
       <c r="C29" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D29" s="1">
-        <v>124065256</v>
-      </c>
-      <c r="E29" s="2">
-        <v>86</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
+        <v>85095599</v>
+      </c>
+      <c r="E29" s="1">
+        <v>70</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>10</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
         <v>4</v>
       </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>17</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2">
-        <v>4</v>
-      </c>
       <c r="N29" s="1">
-        <v>10478012</v>
+        <v>16970977</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1862,40 +1864,40 @@
         <v>24</v>
       </c>
       <c r="C30" s="2">
-        <v>717</v>
+        <v>603</v>
       </c>
       <c r="D30" s="1">
-        <v>10546155872</v>
-      </c>
-      <c r="E30" s="2">
-        <v>802</v>
-      </c>
-      <c r="F30" s="2">
-        <v>2</v>
-      </c>
-      <c r="G30" s="2">
-        <v>7</v>
-      </c>
-      <c r="H30" s="2">
-        <v>23</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>48</v>
-      </c>
-      <c r="K30" s="2">
-        <v>5</v>
+        <v>10025508752</v>
+      </c>
+      <c r="E30" s="1">
+        <v>692</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>9</v>
+      </c>
+      <c r="H30" s="1">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>16</v>
+      </c>
+      <c r="K30" s="1">
+        <v>3</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
       </c>
-      <c r="M30" s="2">
-        <v>73</v>
+      <c r="M30" s="1">
+        <v>57</v>
       </c>
       <c r="N30" s="1">
-        <v>462033934</v>
+        <v>277212215</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1906,40 +1908,40 @@
         <v>25</v>
       </c>
       <c r="C31" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D31" s="1">
-        <v>153071312</v>
-      </c>
-      <c r="E31" s="2">
-        <v>55</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
-        <v>21</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
+        <v>204566027</v>
+      </c>
+      <c r="E31" s="1">
+        <v>42</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
         <v>4</v>
       </c>
-      <c r="K31" s="2">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2">
-        <v>4</v>
-      </c>
       <c r="N31" s="1">
-        <v>18400859</v>
+        <v>8647442</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1950,40 +1952,40 @@
         <v>26</v>
       </c>
       <c r="C32" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D32" s="1">
-        <v>77232650</v>
-      </c>
-      <c r="E32" s="2">
-        <v>92</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
-        <v>16</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
+        <v>64900947</v>
+      </c>
+      <c r="E32" s="1">
+        <v>53</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>7</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>6957531</v>
-      </c>
-      <c r="M32" s="2">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>3</v>
       </c>
       <c r="N32" s="1">
-        <v>16500980</v>
+        <v>23392346</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1994,40 +1996,40 @@
         <v>27</v>
       </c>
       <c r="C33" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D33" s="1">
-        <v>436786980</v>
-      </c>
-      <c r="E33" s="2">
-        <v>170</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2">
+        <v>377792432</v>
+      </c>
+      <c r="E33" s="1">
+        <v>109</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>3</v>
       </c>
-      <c r="H33" s="2">
-        <v>6</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>12</v>
-      </c>
-      <c r="K33" s="2">
-        <v>0</v>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>8</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2">
-        <v>13</v>
+        <v>1719582</v>
+      </c>
+      <c r="M33" s="1">
+        <v>10</v>
       </c>
       <c r="N33" s="1">
-        <v>40487772</v>
+        <v>31865128</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2038,40 +2040,40 @@
         <v>28</v>
       </c>
       <c r="C34" s="2">
-        <v>459</v>
+        <v>268</v>
       </c>
       <c r="D34" s="1">
-        <v>4478589261</v>
-      </c>
-      <c r="E34" s="2">
-        <v>564</v>
-      </c>
-      <c r="F34" s="2">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2">
-        <v>8</v>
-      </c>
-      <c r="H34" s="2">
-        <v>44</v>
-      </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
-        <v>34</v>
-      </c>
-      <c r="K34" s="2">
-        <v>7</v>
+        <v>3105775161</v>
+      </c>
+      <c r="E34" s="1">
+        <v>357</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1">
+        <v>27</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>10</v>
+      </c>
+      <c r="K34" s="1">
+        <v>4</v>
       </c>
       <c r="L34" s="1">
-        <v>19779818</v>
-      </c>
-      <c r="M34" s="2">
-        <v>59</v>
+        <v>28947273</v>
+      </c>
+      <c r="M34" s="1">
+        <v>32</v>
       </c>
       <c r="N34" s="1">
-        <v>356174098</v>
+        <v>183754009</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2082,40 +2084,40 @@
         <v>29</v>
       </c>
       <c r="C35" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="D35" s="1">
-        <v>3276839120</v>
-      </c>
-      <c r="E35" s="2">
-        <v>620</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2">
-        <v>7</v>
-      </c>
-      <c r="H35" s="2">
-        <v>73</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
-        <v>59</v>
-      </c>
-      <c r="K35" s="2">
-        <v>7</v>
+        <v>4073752152</v>
+      </c>
+      <c r="E35" s="1">
+        <v>445</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
+        <v>36</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>34</v>
+      </c>
+      <c r="K35" s="1">
+        <v>3</v>
       </c>
       <c r="L35" s="1">
-        <v>34402502</v>
-      </c>
-      <c r="M35" s="2">
-        <v>52</v>
+        <v>10861894</v>
+      </c>
+      <c r="M35" s="1">
+        <v>48</v>
       </c>
       <c r="N35" s="1">
-        <v>265240164</v>
+        <v>258517543</v>
       </c>
     </row>
   </sheetData>
